--- a/tests/perf_v2/perf_history/v2.4.2/detection/DETECTION-raw-visdrone.xlsx
+++ b/tests/perf_v2/perf_history/v2.4.2/detection/DETECTION-raw-visdrone.xlsx
@@ -9,15 +9,16 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_mobilenetv2" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_resnext101" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_101" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_18" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_50" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtmdet_tiny" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ssd_mobilenetv2" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_l" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_s" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_tiny" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_x" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dfine_x" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_101" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_18" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_50" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtmdet_tiny" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ssd_mobilenetv2" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_l" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_s" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_tiny" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_x" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1416,62 +1417,62 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C2" t="n">
-        <v>3079.322563171387</v>
+        <v>3769.914018630981</v>
       </c>
       <c r="D2" t="n">
-        <v>6.739999771118164</v>
+        <v>7.809999942779541</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1644976583700025</v>
+        <v>0.2099228995541731</v>
       </c>
       <c r="F2" t="n">
-        <v>0.364290326833725</v>
+        <v>0.5128582119941711</v>
       </c>
       <c r="G2" t="n">
-        <v>0.343667209148407</v>
+        <v>0.4817813634872436</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3442384600639343</v>
+        <v>0.4831418693065643</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3389679789543152</v>
+        <v>0.4801167249679565</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0582591407001018</v>
+        <v>0.0829966366291046</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9983993768692015</v>
+        <v>1.258856058120728</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9700360298156738</v>
+        <v>1.035138845443726</v>
       </c>
       <c r="M2" t="n">
-        <v>34.33331108093262</v>
+        <v>59.08326888084412</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0248484102884928</v>
+        <v>0.0350144664446512</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0528407923380533</v>
+        <v>0.0627606201171875</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0514014299710591</v>
+        <v>0.0595352506637573</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.454523086547852</v>
+        <v>10.50433993339539</v>
       </c>
       <c r="R2" t="n">
-        <v>15.85223770141602</v>
+        <v>18.82818603515625</v>
       </c>
       <c r="S2" t="n">
-        <v>15.42042899131775</v>
+        <v>17.8605751991272</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>20250516-091859</t>
+          <t>20250509-045803</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -1481,7 +1482,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>yolox_tiny</t>
+          <t>yolox_s</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -1501,7 +1502,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>f3410bbc1</t>
+          <t>97feded0d</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -1511,7 +1512,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>f3410bbc1</t>
+          <t>97feded0d</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1546,59 +1547,59 @@
         <v>83</v>
       </c>
       <c r="C3" t="n">
-        <v>4119.050171375275</v>
+        <v>5086.055543661118</v>
       </c>
       <c r="D3" t="n">
-        <v>5.110000133514404</v>
+        <v>9.75</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1649785991533693</v>
+        <v>0.2083594913942268</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3747325241565704</v>
+        <v>0.52392578125</v>
       </c>
       <c r="G3" t="n">
-        <v>0.355275422334671</v>
+        <v>0.4936708807945251</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3539822995662689</v>
+        <v>0.4936651885509491</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3478068113327026</v>
+        <v>0.4914116263389587</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0583103112876415</v>
+        <v>0.0859270095825195</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9244027733802797</v>
+        <v>1.26954996585846</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9738867878913881</v>
+        <v>1.080401420593261</v>
       </c>
       <c r="M3" t="n">
-        <v>34.81492376327515</v>
+        <v>58.35318040847778</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0249835197130839</v>
+        <v>0.0364483650525411</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0545999646186828</v>
+        <v>0.0634031629562378</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0523309747378031</v>
+        <v>0.0611013825734456</v>
       </c>
       <c r="Q3" t="n">
-        <v>7.495055913925171</v>
+        <v>10.93450951576233</v>
       </c>
       <c r="R3" t="n">
-        <v>16.37998938560486</v>
+        <v>19.02094888687133</v>
       </c>
       <c r="S3" t="n">
-        <v>15.69929242134094</v>
+        <v>18.33041477203369</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>20250516-101225</t>
+          <t>20250509-060335</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -1608,7 +1609,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>yolox_tiny</t>
+          <t>yolox_s</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1628,7 +1629,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>f3410bbc1</t>
+          <t>97feded0d</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1638,7 +1639,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>f3410bbc1</t>
+          <t>97feded0d</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1670,62 +1671,62 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="C4" t="n">
-        <v>2184.960909128189</v>
+        <v>3482.002310276031</v>
       </c>
       <c r="D4" t="n">
-        <v>6.320000171661377</v>
+        <v>8.800000190734863</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1640736724842678</v>
+        <v>0.2111128784183945</v>
       </c>
       <c r="F4" t="n">
-        <v>0.355081707239151</v>
+        <v>0.5099393129348755</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3354832828044891</v>
+        <v>0.4790474474430084</v>
       </c>
       <c r="H4" t="n">
-        <v>0.339835375547409</v>
+        <v>0.4799931943416595</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3301154673099518</v>
+        <v>0.4775107204914093</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0581402331590652</v>
+        <v>0.0875294283032417</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9395607113838196</v>
+        <v>1.262146353721619</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9786917567253112</v>
+        <v>1.04424238204956</v>
       </c>
       <c r="M4" t="n">
-        <v>34.74675726890564</v>
+        <v>60.39233493804932</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0241434383392333</v>
+        <v>0.0343831793467203</v>
       </c>
       <c r="O4" t="n">
-        <v>0.051514147122701</v>
+        <v>0.06392911672592159</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0509887965520223</v>
+        <v>0.0593721763292948</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.24303150177002</v>
+        <v>10.31495380401611</v>
       </c>
       <c r="R4" t="n">
-        <v>15.4542441368103</v>
+        <v>19.17873501777649</v>
       </c>
       <c r="S4" t="n">
-        <v>15.29663896560669</v>
+        <v>17.81165289878845</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>20250516-112312</t>
+          <t>20250509-073103</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -1735,7 +1736,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>yolox_tiny</t>
+          <t>yolox_s</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1755,7 +1756,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>f3410bbc1</t>
+          <t>97feded0d</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1765,7 +1766,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>f3410bbc1</t>
+          <t>97feded0d</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1797,62 +1798,62 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="C5" t="n">
-        <v>3154.34850692749</v>
+        <v>4894.750937700272</v>
       </c>
       <c r="D5" t="n">
-        <v>5.349999904632568</v>
+        <v>9.020000457763672</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1633750172331928</v>
+        <v>0.2063441587612033</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3684252798557281</v>
+        <v>0.5092978477478027</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3486214578151703</v>
+        <v>0.4746448695659637</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3518382012844085</v>
+        <v>0.4786581695079803</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3449382185935974</v>
+        <v>0.474529355764389</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0582641437649726</v>
+        <v>0.0810377821326255</v>
       </c>
       <c r="K5" t="n">
-        <v>0.911863088607788</v>
+        <v>1.338886857032776</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9335759878158568</v>
+        <v>1.06293535232544</v>
       </c>
       <c r="M5" t="n">
-        <v>34.33284592628479</v>
+        <v>58.31261396408081</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0254259546597798</v>
+        <v>0.0343996143341064</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0521444257100423</v>
+        <v>0.0655732154846191</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0513861481348673</v>
+        <v>0.0612890243530273</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.62778639793396</v>
+        <v>10.31988430023193</v>
       </c>
       <c r="R5" t="n">
-        <v>15.6433277130127</v>
+        <v>19.67196464538575</v>
       </c>
       <c r="S5" t="n">
-        <v>15.4158444404602</v>
+        <v>18.3867073059082</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>20250516-120143</t>
+          <t>20250509-083147</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1862,7 +1863,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>yolox_tiny</t>
+          <t>yolox_s</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1882,7 +1883,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>f3410bbc1</t>
+          <t>97feded0d</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1892,7 +1893,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>f3410bbc1</t>
+          <t>97feded0d</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1924,62 +1925,62 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="C6" t="n">
-        <v>2038.435772657394</v>
+        <v>3476.170988798141</v>
       </c>
       <c r="D6" t="n">
-        <v>5.480000019073486</v>
+        <v>6.019999980926514</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1643663023303194</v>
+        <v>0.2091836777648755</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3437761068344116</v>
+        <v>0.5107935667037964</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3247758448123932</v>
+        <v>0.4730213582515716</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3286438286304474</v>
+        <v>0.476974606513977</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3256403505802154</v>
+        <v>0.4722312688827514</v>
       </c>
       <c r="J6" t="n">
-        <v>0.05673049390316</v>
+        <v>0.0856380313634872</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9328705072402954</v>
+        <v>1.247788906097412</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9635183215141296</v>
+        <v>1.058021545410156</v>
       </c>
       <c r="M6" t="n">
-        <v>34.41638493537903</v>
+        <v>60.08119416236877</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0253148460388183</v>
+        <v>0.0353939541180928</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0505043498675028</v>
+        <v>0.0639199225107828</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0509190861384073</v>
+        <v>0.059868570168813</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.594453811645508</v>
+        <v>10.61818623542786</v>
       </c>
       <c r="R6" t="n">
-        <v>15.15130496025085</v>
+        <v>19.17597675323486</v>
       </c>
       <c r="S6" t="n">
-        <v>15.27572584152222</v>
+        <v>17.96057105064392</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>20250516-125624</t>
+          <t>20250509-095604</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1989,7 +1990,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>yolox_tiny</t>
+          <t>yolox_s</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2009,7 +2010,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>f3410bbc1</t>
+          <t>97feded0d</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -2019,7 +2020,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>f3410bbc1</t>
+          <t>97feded0d</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -2227,6 +2228,817 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
+        <v>62</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3079.322563171387</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6.739999771118164</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.1644976583700025</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.364290326833725</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.343667209148407</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.3442384600639343</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.3389679789543152</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0582591407001018</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.9983993768692015</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.9700360298156738</v>
+      </c>
+      <c r="M2" t="n">
+        <v>34.33331108093262</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.0248484102884928</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0528407923380533</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.0514014299710591</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>7.454523086547852</v>
+      </c>
+      <c r="R2" t="n">
+        <v>15.85223770141602</v>
+      </c>
+      <c r="S2" t="n">
+        <v>15.42042899131775</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>20250516-091859</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>DETECTION</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>yolox_tiny</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>visdrone</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2.4.2</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>f3410bbc1</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>eugene/2.4.2-det-benchmark</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>f3410bbc1</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>workstation06</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>83</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4119.050171375275</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5.110000133514404</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1649785991533693</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3747325241565704</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.355275422334671</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.3539822995662689</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.3478068113327026</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.0583103112876415</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.9244027733802797</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.9738867878913881</v>
+      </c>
+      <c r="M3" t="n">
+        <v>34.81492376327515</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.0249835197130839</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0545999646186828</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.0523309747378031</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>7.495055913925171</v>
+      </c>
+      <c r="R3" t="n">
+        <v>16.37998938560486</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15.69929242134094</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>20250516-101225</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>DETECTION</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>yolox_tiny</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>visdrone</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2.4.2</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>f3410bbc1</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>eugene/2.4.2-det-benchmark</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>f3410bbc1</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>workstation06</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>44</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2184.960909128189</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.320000171661377</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1640736724842678</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.355081707239151</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.3354832828044891</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.339835375547409</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.3301154673099518</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.0581402331590652</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.9395607113838196</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.9786917567253112</v>
+      </c>
+      <c r="M4" t="n">
+        <v>34.74675726890564</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.0241434383392333</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.051514147122701</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.0509887965520223</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>7.24303150177002</v>
+      </c>
+      <c r="R4" t="n">
+        <v>15.4542441368103</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15.29663896560669</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>20250516-112312</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>DETECTION</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>yolox_tiny</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>visdrone</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2.4.2</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>f3410bbc1</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>eugene/2.4.2-det-benchmark</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>f3410bbc1</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>workstation06</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>64</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3154.34850692749</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5.349999904632568</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.1633750172331928</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3684252798557281</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.3486214578151703</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.3518382012844085</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.3449382185935974</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.0582641437649726</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.911863088607788</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.9335759878158568</v>
+      </c>
+      <c r="M5" t="n">
+        <v>34.33284592628479</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.0254259546597798</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0521444257100423</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.0513861481348673</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>7.62778639793396</v>
+      </c>
+      <c r="R5" t="n">
+        <v>15.6433277130127</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15.4158444404602</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>20250516-120143</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>DETECTION</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>yolox_tiny</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>visdrone</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2.4.2</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>f3410bbc1</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>eugene/2.4.2-det-benchmark</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>f3410bbc1</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>workstation06</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>41</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2038.435772657394</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5.480000019073486</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.1643663023303194</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.3437761068344116</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.3247758448123932</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.3286438286304474</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.3256403505802154</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.05673049390316</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.9328705072402954</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.9635183215141296</v>
+      </c>
+      <c r="M6" t="n">
+        <v>34.41638493537903</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.0253148460388183</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0505043498675028</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.0509190861384073</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>7.594453811645508</v>
+      </c>
+      <c r="R6" t="n">
+        <v>15.15130496025085</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15.27572584152222</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>20250516-125624</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>DETECTION</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>yolox_tiny</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>visdrone</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2.4.2</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>f3410bbc1</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>eugene/2.4.2-det-benchmark</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>f3410bbc1</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>workstation06</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>training:epoch</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>training:e2e_time</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>training:gpu_mem</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>training:train/iter_time</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>training:val/f1-score</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/f1-score</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>export:test/f1-score</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>optimize:test/f1-score</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/iter_time</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>export:test/iter_time</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimize:test/iter_time</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>optimize:e2e_time</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/latency</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>export:test/latency</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimize:test/latency</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/e2e_time</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>export:test/e2e_time</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>optimize:test/e2e_time</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>task</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>data_group</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>otx_version</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>otx_ref</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>test_branch</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>test_commit</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>cpu_info</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>accelerator_info</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>user_name</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>machine_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
         <v>48</v>
       </c>
       <c r="C2" t="n">
@@ -3849,62 +4661,62 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="C2" t="n">
-        <v>5221.704950332642</v>
+        <v>6778.71887087822</v>
       </c>
       <c r="D2" t="n">
-        <v>15.90999984741211</v>
+        <v>18.79000091552734</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3177236487736573</v>
+        <v>0.5481423551386053</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6237346529960632</v>
+        <v>0.6256076693534851</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5890452861785889</v>
+        <v>0.5911568403244019</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5912254452705383</v>
+        <v>0.5918735265731812</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5797112584114075</v>
+        <v>0.5836381316184998</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1232470050454139</v>
+        <v>0.1117441281676292</v>
       </c>
       <c r="K2" t="n">
-        <v>9.485721588134766</v>
+        <v>7.497416973114014</v>
       </c>
       <c r="L2" t="n">
-        <v>3.914522886276245</v>
+        <v>2.939783573150635</v>
       </c>
       <c r="M2" t="n">
-        <v>306.601535320282</v>
+        <v>1131.401929855347</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0559373068809509</v>
+        <v>0.0516059271494547</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2120527974764506</v>
+        <v>0.1810310753186543</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1255707955360412</v>
+        <v>0.1145434339841206</v>
       </c>
       <c r="Q2" t="n">
-        <v>16.78119206428528</v>
+        <v>15.48177814483643</v>
       </c>
       <c r="R2" t="n">
-        <v>63.61583924293518</v>
+        <v>54.30932259559631</v>
       </c>
       <c r="S2" t="n">
-        <v>37.67123866081238</v>
+        <v>34.36303019523621</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>20250513-141312</t>
+          <t>20250710-125751</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -3914,7 +4726,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -3934,17 +4746,17 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>f3410bbc1</t>
+          <t>b7a58e7dd</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>eugene/2.4.2-det-benchmark</t>
+          <t>eugene/benchmark/2.4.2</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>f3410bbc1</t>
+          <t>b7a58e7dd</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -3976,62 +4788,62 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="C3" t="n">
-        <v>6685.745876789093</v>
+        <v>9362.851414680479</v>
       </c>
       <c r="D3" t="n">
-        <v>17.72999954223633</v>
+        <v>18.35000038146973</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3150506851573785</v>
+        <v>0.5459197493823799</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6306551694869995</v>
+        <v>0.6378837823867798</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5979152917861938</v>
+        <v>0.6022199988365173</v>
       </c>
       <c r="H3" t="n">
-        <v>0.598771333694458</v>
+        <v>0.6031840443611145</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5915178656578064</v>
+        <v>0.5995821356773376</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1198949441313743</v>
+        <v>0.1144055798649787</v>
       </c>
       <c r="K3" t="n">
-        <v>9.55189037322998</v>
+        <v>7.455558300018311</v>
       </c>
       <c r="L3" t="n">
-        <v>3.859420537948608</v>
+        <v>2.932513236999512</v>
       </c>
       <c r="M3" t="n">
-        <v>314.3156275749207</v>
+        <v>1135.78475356102</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0578804763158162</v>
+        <v>0.052666441599528</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2127313748995463</v>
+        <v>0.1802308257420857</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1261457101504008</v>
+        <v>0.11552627881368</v>
       </c>
       <c r="Q3" t="n">
-        <v>17.36414289474487</v>
+        <v>15.7999324798584</v>
       </c>
       <c r="R3" t="n">
-        <v>63.81941246986389</v>
+        <v>54.06924772262573</v>
       </c>
       <c r="S3" t="n">
-        <v>37.84371304512024</v>
+        <v>34.657883644104</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>20250513-154848</t>
+          <t>20250710-151249</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -4041,7 +4853,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -4061,17 +4873,17 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>f3410bbc1</t>
+          <t>b7a58e7dd</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>eugene/2.4.2-det-benchmark</t>
+          <t>eugene/benchmark/2.4.2</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>f3410bbc1</t>
+          <t>b7a58e7dd</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -4103,62 +4915,62 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C4" t="n">
-        <v>5359.67647767067</v>
+        <v>2605.106190919876</v>
       </c>
       <c r="D4" t="n">
-        <v>18.31999969482422</v>
+        <v>15.8100004196167</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3166422522381732</v>
+        <v>0.551096240679423</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6312329173088074</v>
+        <v>0.5778452157974243</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5913388133049011</v>
+        <v>0.5352758765220642</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5912904143333435</v>
+        <v>0.5359886884689331</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5865893959999084</v>
+        <v>0.5309085249900818</v>
       </c>
       <c r="J4" t="n">
-        <v>0.12248545140028</v>
+        <v>0.1160249933600425</v>
       </c>
       <c r="K4" t="n">
-        <v>9.408479690551758</v>
+        <v>7.454716205596924</v>
       </c>
       <c r="L4" t="n">
-        <v>3.862648963928223</v>
+        <v>2.881789445877075</v>
       </c>
       <c r="M4" t="n">
-        <v>326.8483991622925</v>
+        <v>1135.185162305832</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0574344905217488</v>
+        <v>0.0501004528999328</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2128107070922851</v>
+        <v>0.1771891967455546</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1264657084147135</v>
+        <v>0.1130322774251302</v>
       </c>
       <c r="Q4" t="n">
-        <v>17.23034715652466</v>
+        <v>15.03013586997986</v>
       </c>
       <c r="R4" t="n">
-        <v>63.84321212768555</v>
+        <v>53.15675902366638</v>
       </c>
       <c r="S4" t="n">
-        <v>37.93971252441406</v>
+        <v>33.90968322753906</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>20250513-174857</t>
+          <t>20250710-181056</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -4168,7 +4980,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -4188,17 +5000,17 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>f3410bbc1</t>
+          <t>b7a58e7dd</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>eugene/2.4.2-det-benchmark</t>
+          <t>eugene/benchmark/2.4.2</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>f3410bbc1</t>
+          <t>b7a58e7dd</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -4230,62 +5042,62 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C5" t="n">
-        <v>7231.645013809204</v>
+        <v>7585.45571064949</v>
       </c>
       <c r="D5" t="n">
-        <v>17.40999984741211</v>
+        <v>17.8700008392334</v>
       </c>
       <c r="E5" t="n">
-        <v>0.313907968883331</v>
+        <v>0.5478618651628494</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6291422247886658</v>
+        <v>0.6312968730926514</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5970642566680908</v>
+        <v>0.5934686660766602</v>
       </c>
       <c r="H5" t="n">
-        <v>0.59688401222229</v>
+        <v>0.5942360758781433</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5913850665092468</v>
+        <v>0.5904457569122314</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1213735938072204</v>
+        <v>0.1181453838944435</v>
       </c>
       <c r="K5" t="n">
-        <v>9.439741134643556</v>
+        <v>7.577322483062744</v>
       </c>
       <c r="L5" t="n">
-        <v>3.888901472091675</v>
+        <v>2.980899333953857</v>
       </c>
       <c r="M5" t="n">
-        <v>321.3581960201263</v>
+        <v>1133.194477796555</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0565734124183654</v>
+        <v>0.0517621715863545</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2109926104545593</v>
+        <v>0.1806409533818563</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1255219483375549</v>
+        <v>0.1148651512463887</v>
       </c>
       <c r="Q5" t="n">
-        <v>16.97202372550964</v>
+        <v>15.52865147590637</v>
       </c>
       <c r="R5" t="n">
-        <v>63.2977831363678</v>
+        <v>54.19228601455688</v>
       </c>
       <c r="S5" t="n">
-        <v>37.65658450126648</v>
+        <v>34.45954537391663</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>20250513-192715</t>
+          <t>20250711-110350</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -4295,7 +5107,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -4315,17 +5127,17 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>f3410bbc1</t>
+          <t>b7a58e7dd</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>eugene/2.4.2-det-benchmark</t>
+          <t>eugene/benchmark/2.4.2</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>f3410bbc1</t>
+          <t>b7a58e7dd</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -4357,62 +5169,62 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C6" t="n">
-        <v>6928.485826015472</v>
+        <v>6761.453576087952</v>
       </c>
       <c r="D6" t="n">
-        <v>17.32999992370605</v>
+        <v>17.79999923706055</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3136815595626831</v>
+        <v>0.5537657483860299</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6294952630996704</v>
+        <v>0.6294155120849609</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5929193496704102</v>
+        <v>0.5932988524436951</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5924332737922668</v>
+        <v>0.5936872959136963</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5859278440475464</v>
+        <v>0.5887162089347839</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1239261925220489</v>
+        <v>0.11783979088068</v>
       </c>
       <c r="K6" t="n">
-        <v>9.538196563720703</v>
+        <v>7.534725666046143</v>
       </c>
       <c r="L6" t="n">
-        <v>3.900332450866699</v>
+        <v>2.907919883728028</v>
       </c>
       <c r="M6" t="n">
-        <v>339.7148959636688</v>
+        <v>1137.198942661285</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0563911509513855</v>
+        <v>0.0510823806126912</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2119166278839111</v>
+        <v>0.1787739062309265</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1262154340744018</v>
+        <v>0.1144043612480163</v>
       </c>
       <c r="Q6" t="n">
-        <v>16.91734528541565</v>
+        <v>15.32471418380737</v>
       </c>
       <c r="R6" t="n">
-        <v>63.57498836517334</v>
+        <v>53.63217186927795</v>
       </c>
       <c r="S6" t="n">
-        <v>37.86463022232056</v>
+        <v>34.32130837440491</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>20250513-213634</t>
+          <t>20250711-133219</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -4422,7 +5234,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -4442,17 +5254,17 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>f3410bbc1</t>
+          <t>b7a58e7dd</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>eugene/2.4.2-det-benchmark</t>
+          <t>eugene/benchmark/2.4.2</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>f3410bbc1</t>
+          <t>b7a58e7dd</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -4660,62 +5472,62 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="C2" t="n">
-        <v>9765.824536085129</v>
+        <v>5221.704950332642</v>
       </c>
       <c r="D2" t="n">
-        <v>7.360000133514404</v>
+        <v>15.90999984741211</v>
       </c>
       <c r="E2" t="n">
-        <v>0.278589040795459</v>
+        <v>0.3177236487736573</v>
       </c>
       <c r="F2" t="n">
-        <v>0.587872326374054</v>
+        <v>0.6237346529960632</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5593848824501038</v>
+        <v>0.5890452861785889</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5596014857292175</v>
+        <v>0.5912254452705383</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5485451817512512</v>
+        <v>0.5797112584114075</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1155405566096305</v>
+        <v>0.1232470050454139</v>
       </c>
       <c r="K2" t="n">
-        <v>2.283823251724243</v>
+        <v>9.485721588134766</v>
       </c>
       <c r="L2" t="n">
-        <v>1.396850943565369</v>
+        <v>3.914522886276245</v>
       </c>
       <c r="M2" t="n">
-        <v>113.6678404808044</v>
+        <v>306.601535320282</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0463956665992736</v>
+        <v>0.0559373068809509</v>
       </c>
       <c r="O2" t="n">
-        <v>0.089038454691569</v>
+        <v>0.2120527974764506</v>
       </c>
       <c r="P2" t="n">
-        <v>0.076496299902598</v>
+        <v>0.1255707955360412</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.9186999797821</v>
+        <v>16.78119206428528</v>
       </c>
       <c r="R2" t="n">
-        <v>26.7115364074707</v>
+        <v>63.61583924293518</v>
       </c>
       <c r="S2" t="n">
-        <v>22.94888997077942</v>
+        <v>37.67123866081238</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>20250514-064928</t>
+          <t>20250513-141312</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -4725,7 +5537,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -4787,62 +5599,62 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="C3" t="n">
-        <v>8041.210235834122</v>
+        <v>6685.745876789093</v>
       </c>
       <c r="D3" t="n">
-        <v>8.130000114440918</v>
+        <v>17.72999954223633</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2839062931016087</v>
+        <v>0.3150506851573785</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5835606455802917</v>
+        <v>0.6306551694869995</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5570592284202576</v>
+        <v>0.5979152917861938</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5572956800460815</v>
+        <v>0.598771333694458</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5476652979850769</v>
+        <v>0.5915178656578064</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1079262271523475</v>
+        <v>0.1198949441313743</v>
       </c>
       <c r="K3" t="n">
-        <v>2.269658088684082</v>
+        <v>9.55189037322998</v>
       </c>
       <c r="L3" t="n">
-        <v>1.346625208854675</v>
+        <v>3.859420537948608</v>
       </c>
       <c r="M3" t="n">
-        <v>112.8661937713623</v>
+        <v>314.3156275749207</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0446715513865153</v>
+        <v>0.0578804763158162</v>
       </c>
       <c r="O3" t="n">
-        <v>0.08781486352284749</v>
+        <v>0.2127313748995463</v>
       </c>
       <c r="P3" t="n">
-        <v>0.07642371575037631</v>
+        <v>0.1261457101504008</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.40146541595459</v>
+        <v>17.36414289474487</v>
       </c>
       <c r="R3" t="n">
-        <v>26.34445905685425</v>
+        <v>63.81941246986389</v>
       </c>
       <c r="S3" t="n">
-        <v>22.92711472511292</v>
+        <v>37.84371304512024</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>20250514-093613</t>
+          <t>20250513-154848</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -4852,7 +5664,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -4914,62 +5726,62 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="C4" t="n">
-        <v>9194.285727739334</v>
+        <v>5359.67647767067</v>
       </c>
       <c r="D4" t="n">
-        <v>8.170000076293945</v>
+        <v>18.31999969482422</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2916655387315485</v>
+        <v>0.3166422522381732</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5867528915405273</v>
+        <v>0.6312329173088074</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5585964918136597</v>
+        <v>0.5913388133049011</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5577664375305176</v>
+        <v>0.5912904143333435</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5491397380828857</v>
+        <v>0.5865893959999084</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1113433018326759</v>
+        <v>0.12248545140028</v>
       </c>
       <c r="K4" t="n">
-        <v>2.277013778686523</v>
+        <v>9.408479690551758</v>
       </c>
       <c r="L4" t="n">
-        <v>1.388325572013855</v>
+        <v>3.862648963928223</v>
       </c>
       <c r="M4" t="n">
-        <v>111.2087848186493</v>
+        <v>326.8483991622925</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0454032071431477</v>
+        <v>0.0574344905217488</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0890786298116048</v>
+        <v>0.2128107070922851</v>
       </c>
       <c r="P4" t="n">
-        <v>0.07594580968221019</v>
+        <v>0.1264657084147135</v>
       </c>
       <c r="Q4" t="n">
-        <v>13.62096214294434</v>
+        <v>17.23034715652466</v>
       </c>
       <c r="R4" t="n">
-        <v>26.72358894348145</v>
+        <v>63.84321212768555</v>
       </c>
       <c r="S4" t="n">
-        <v>22.78374290466309</v>
+        <v>37.93971252441406</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>20250514-115412</t>
+          <t>20250513-174857</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -4979,7 +5791,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -5044,59 +5856,59 @@
         <v>52</v>
       </c>
       <c r="C5" t="n">
-        <v>6577.0746986866</v>
+        <v>7231.645013809204</v>
       </c>
       <c r="D5" t="n">
-        <v>8.199999809265137</v>
+        <v>17.40999984741211</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2842732335512454</v>
+        <v>0.313907968883331</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5790687203407288</v>
+        <v>0.6291422247886658</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5518223643302917</v>
+        <v>0.5970642566680908</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5508650541305542</v>
+        <v>0.59688401222229</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5382114052772522</v>
+        <v>0.5913850665092468</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1127315312623977</v>
+        <v>0.1213735938072204</v>
       </c>
       <c r="K5" t="n">
-        <v>2.314394474029541</v>
+        <v>9.439741134643556</v>
       </c>
       <c r="L5" t="n">
-        <v>1.35684871673584</v>
+        <v>3.888901472091675</v>
       </c>
       <c r="M5" t="n">
-        <v>112.9643394947052</v>
+        <v>321.3581960201263</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0458720143636067</v>
+        <v>0.0565734124183654</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0879399466514587</v>
+        <v>0.2109926104545593</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0753359691301981</v>
+        <v>0.1255219483375549</v>
       </c>
       <c r="Q5" t="n">
-        <v>13.76160430908203</v>
+        <v>16.97202372550964</v>
       </c>
       <c r="R5" t="n">
-        <v>26.38198399543763</v>
+        <v>63.2977831363678</v>
       </c>
       <c r="S5" t="n">
-        <v>22.60079073905945</v>
+        <v>37.65658450126648</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>20250514-143124</t>
+          <t>20250513-192715</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -5106,7 +5918,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -5168,62 +5980,62 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>9003.390444040298</v>
+        <v>6928.485826015472</v>
       </c>
       <c r="D6" t="n">
-        <v>8.289999961853027</v>
+        <v>17.32999992370605</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2888123090838043</v>
+        <v>0.3136815595626831</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5860996246337891</v>
+        <v>0.6294952630996704</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5558674335479736</v>
+        <v>0.5929193496704102</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5561705827713013</v>
+        <v>0.5924332737922668</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5438130497932434</v>
+        <v>0.5859278440475464</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1106986105442047</v>
+        <v>0.1239261925220489</v>
       </c>
       <c r="K6" t="n">
-        <v>2.290555715560913</v>
+        <v>9.538196563720703</v>
       </c>
       <c r="L6" t="n">
-        <v>1.41083574295044</v>
+        <v>3.900332450866699</v>
       </c>
       <c r="M6" t="n">
-        <v>112.752854347229</v>
+        <v>339.7148959636688</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0457181390126546</v>
+        <v>0.0563911509513855</v>
       </c>
       <c r="O6" t="n">
-        <v>0.08883585850397741</v>
+        <v>0.2119166278839111</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0766776990890503</v>
+        <v>0.1262154340744018</v>
       </c>
       <c r="Q6" t="n">
-        <v>13.71544170379639</v>
+        <v>16.91734528541565</v>
       </c>
       <c r="R6" t="n">
-        <v>26.65075755119324</v>
+        <v>63.57498836517334</v>
       </c>
       <c r="S6" t="n">
-        <v>23.00330972671509</v>
+        <v>37.86463022232056</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>20250514-162501</t>
+          <t>20250513-213634</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -5233,7 +6045,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -5471,62 +6283,62 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="C2" t="n">
-        <v>5188.552840232849</v>
+        <v>9765.824536085129</v>
       </c>
       <c r="D2" t="n">
-        <v>13.56999969482422</v>
+        <v>7.360000133514404</v>
       </c>
       <c r="E2" t="n">
-        <v>0.280188864324151</v>
+        <v>0.278589040795459</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6287190914154053</v>
+        <v>0.587872326374054</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5828397870063782</v>
+        <v>0.5593848824501038</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5835258364677429</v>
+        <v>0.5596014857292175</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5697336196899414</v>
+        <v>0.5485451817512512</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1125752702355384</v>
+        <v>0.1155405566096305</v>
       </c>
       <c r="K2" t="n">
-        <v>4.937784194946289</v>
+        <v>2.283823251724243</v>
       </c>
       <c r="L2" t="n">
-        <v>2.812518835067749</v>
+        <v>1.396850943565369</v>
       </c>
       <c r="M2" t="n">
-        <v>248.6223483085632</v>
+        <v>113.6678404808044</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0496481895446777</v>
+        <v>0.0463956665992736</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1351320465405782</v>
+        <v>0.089038454691569</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1033555364608764</v>
+        <v>0.076496299902598</v>
       </c>
       <c r="Q2" t="n">
-        <v>14.89445686340332</v>
+        <v>13.9186999797821</v>
       </c>
       <c r="R2" t="n">
-        <v>40.53961396217346</v>
+        <v>26.7115364074707</v>
       </c>
       <c r="S2" t="n">
-        <v>31.00666093826294</v>
+        <v>22.94888997077942</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>20250515-024143</t>
+          <t>20250514-064928</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -5536,7 +6348,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -5598,62 +6410,62 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C3" t="n">
-        <v>6833.83750128746</v>
+        <v>8041.210235834122</v>
       </c>
       <c r="D3" t="n">
-        <v>14.68000030517578</v>
+        <v>8.130000114440918</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2803049622862427</v>
+        <v>0.2839062931016087</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6316810846328735</v>
+        <v>0.5835606455802917</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5997350215911865</v>
+        <v>0.5570592284202576</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5993266105651855</v>
+        <v>0.5572956800460815</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5807638764381409</v>
+        <v>0.5476652979850769</v>
       </c>
       <c r="J3" t="n">
-        <v>0.11391032487154</v>
+        <v>0.1079262271523475</v>
       </c>
       <c r="K3" t="n">
-        <v>4.885299205780029</v>
+        <v>2.269658088684082</v>
       </c>
       <c r="L3" t="n">
-        <v>2.836658477783203</v>
+        <v>1.346625208854675</v>
       </c>
       <c r="M3" t="n">
-        <v>219.612279176712</v>
+        <v>112.8661937713623</v>
       </c>
       <c r="N3" t="n">
-        <v>0.052714360555013</v>
+        <v>0.0446715513865153</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1360075139999389</v>
+        <v>0.08781486352284749</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1073471983273824</v>
+        <v>0.07642371575037631</v>
       </c>
       <c r="Q3" t="n">
-        <v>15.81430816650391</v>
+        <v>13.40146541595459</v>
       </c>
       <c r="R3" t="n">
-        <v>40.80225419998169</v>
+        <v>26.34445905685425</v>
       </c>
       <c r="S3" t="n">
-        <v>32.20415949821472</v>
+        <v>22.92711472511292</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>20250515-041459</t>
+          <t>20250514-093613</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -5663,7 +6475,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -5725,62 +6537,62 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>4764.842020273209</v>
+        <v>9194.285727739334</v>
       </c>
       <c r="D4" t="n">
-        <v>15.81999969482422</v>
+        <v>8.170000076293945</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2752702126377507</v>
+        <v>0.2916655387315485</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6218905448913574</v>
+        <v>0.5867528915405273</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5937235355377197</v>
+        <v>0.5585964918136597</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5947504043579102</v>
+        <v>0.5577664375305176</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5806722044944763</v>
+        <v>0.5491397380828857</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1089552491903305</v>
+        <v>0.1113433018326759</v>
       </c>
       <c r="K4" t="n">
-        <v>4.891057014465332</v>
+        <v>2.277013778686523</v>
       </c>
       <c r="L4" t="n">
-        <v>2.882539510726929</v>
+        <v>1.388325572013855</v>
       </c>
       <c r="M4" t="n">
-        <v>215.2960937023163</v>
+        <v>111.2087848186493</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0496976939837137</v>
+        <v>0.0454032071431477</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1343611256281534</v>
+        <v>0.0890786298116048</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1071430301666259</v>
+        <v>0.07594580968221019</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.90930819511414</v>
+        <v>13.62096214294434</v>
       </c>
       <c r="R4" t="n">
-        <v>40.30833768844604</v>
+        <v>26.72358894348145</v>
       </c>
       <c r="S4" t="n">
-        <v>32.14290904998779</v>
+        <v>22.78374290466309</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>20250515-061515</t>
+          <t>20250514-115412</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -5790,7 +6602,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -5852,62 +6664,62 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C5" t="n">
-        <v>5944.933463096619</v>
+        <v>6577.0746986866</v>
       </c>
       <c r="D5" t="n">
-        <v>14.44999980926514</v>
+        <v>8.199999809265137</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2797835177563606</v>
+        <v>0.2842732335512454</v>
       </c>
       <c r="F5" t="n">
-        <v>0.630143940448761</v>
+        <v>0.5790687203407288</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5923925638198853</v>
+        <v>0.5518223643302917</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5927668213844299</v>
+        <v>0.5508650541305542</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5806848406791687</v>
+        <v>0.5382114052772522</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1121944934129715</v>
+        <v>0.1127315312623977</v>
       </c>
       <c r="K5" t="n">
-        <v>4.915107727050781</v>
+        <v>2.314394474029541</v>
       </c>
       <c r="L5" t="n">
-        <v>2.840914011001587</v>
+        <v>1.35684871673584</v>
       </c>
       <c r="M5" t="n">
-        <v>222.1654608249664</v>
+        <v>112.9643394947052</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0495013872782389</v>
+        <v>0.0458720143636067</v>
       </c>
       <c r="O5" t="n">
-        <v>0.134300041993459</v>
+        <v>0.0879399466514587</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1046868920326233</v>
+        <v>0.0753359691301981</v>
       </c>
       <c r="Q5" t="n">
-        <v>14.85041618347168</v>
+        <v>13.76160430908203</v>
       </c>
       <c r="R5" t="n">
-        <v>40.29001259803772</v>
+        <v>26.38198399543763</v>
       </c>
       <c r="S5" t="n">
-        <v>31.40606760978699</v>
+        <v>22.60079073905945</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>20250515-074054</t>
+          <t>20250514-143124</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -5917,7 +6729,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -5979,62 +6791,62 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="C6" t="n">
-        <v>4986.722508430481</v>
+        <v>9003.390444040298</v>
       </c>
       <c r="D6" t="n">
-        <v>14.43000030517578</v>
+        <v>8.289999961853027</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2840788150445009</v>
+        <v>0.2888123090838043</v>
       </c>
       <c r="F6" t="n">
-        <v>0.625427782535553</v>
+        <v>0.5860996246337891</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5835095047950745</v>
+        <v>0.5558674335479736</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5836887359619141</v>
+        <v>0.5561705827713013</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5693891644477844</v>
+        <v>0.5438130497932434</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1093842238187789</v>
+        <v>0.1106986105442047</v>
       </c>
       <c r="K6" t="n">
-        <v>4.918684959411621</v>
+        <v>2.290555715560913</v>
       </c>
       <c r="L6" t="n">
-        <v>2.833873987197876</v>
+        <v>1.41083574295044</v>
       </c>
       <c r="M6" t="n">
-        <v>219.3778202533722</v>
+        <v>112.752854347229</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0487260349591573</v>
+        <v>0.0457181390126546</v>
       </c>
       <c r="O6" t="n">
-        <v>0.135168703397115</v>
+        <v>0.08883585850397741</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1036297686894734</v>
+        <v>0.0766776990890503</v>
       </c>
       <c r="Q6" t="n">
-        <v>14.61781048774719</v>
+        <v>13.71544170379639</v>
       </c>
       <c r="R6" t="n">
-        <v>40.55061101913452</v>
+        <v>26.65075755119324</v>
       </c>
       <c r="S6" t="n">
-        <v>31.08893060684204</v>
+        <v>23.00330972671509</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>20250515-092619</t>
+          <t>20250514-162501</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -6044,7 +6856,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -6282,62 +7094,62 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C2" t="n">
-        <v>3442.77494597435</v>
+        <v>5188.552840232849</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>13.56999969482422</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2280745281248676</v>
+        <v>0.280188864324151</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4684184491634369</v>
+        <v>0.6287190914154053</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4380539953708648</v>
+        <v>0.5828397870063782</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4426061809062958</v>
+        <v>0.5835258364677429</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4402731657028198</v>
+        <v>0.5697336196899414</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1429133713245391</v>
+        <v>0.1125752702355384</v>
       </c>
       <c r="K2" t="n">
-        <v>1.10968279838562</v>
+        <v>4.937784194946289</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9816176891326904</v>
+        <v>2.812518835067749</v>
       </c>
       <c r="M2" t="n">
-        <v>52.45492577552795</v>
+        <v>248.6223483085632</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0388447141647338</v>
+        <v>0.0496481895446777</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0581852316856384</v>
+        <v>0.1351320465405782</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0559592819213867</v>
+        <v>0.1033555364608764</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.65341424942017</v>
+        <v>14.89445686340332</v>
       </c>
       <c r="R2" t="n">
-        <v>17.45556950569153</v>
+        <v>40.53961396217346</v>
       </c>
       <c r="S2" t="n">
-        <v>16.78778457641602</v>
+        <v>31.00666093826294</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>20250515-140027</t>
+          <t>20250515-024143</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -6347,7 +7159,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -6409,62 +7221,62 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="C3" t="n">
-        <v>6324.202313661575</v>
+        <v>6833.83750128746</v>
       </c>
       <c r="D3" t="n">
-        <v>4.019999980926514</v>
+        <v>14.68000030517578</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2306147572067048</v>
+        <v>0.2803049622862427</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4784103631973266</v>
+        <v>0.6316810846328735</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4475007653236389</v>
+        <v>0.5997350215911865</v>
       </c>
       <c r="H3" t="n">
-        <v>0.451127827167511</v>
+        <v>0.5993266105651855</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4486460983753204</v>
+        <v>0.5807638764381409</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1416954696178436</v>
+        <v>0.11391032487154</v>
       </c>
       <c r="K3" t="n">
-        <v>1.047324538230896</v>
+        <v>4.885299205780029</v>
       </c>
       <c r="L3" t="n">
-        <v>1.013839602470398</v>
+        <v>2.836658477783203</v>
       </c>
       <c r="M3" t="n">
-        <v>52.26185750961304</v>
+        <v>219.612279176712</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0375942126909891</v>
+        <v>0.052714360555013</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0553642121950785</v>
+        <v>0.1360075139999389</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0553852915763855</v>
+        <v>0.1073471983273824</v>
       </c>
       <c r="Q3" t="n">
-        <v>11.27826380729675</v>
+        <v>15.81430816650391</v>
       </c>
       <c r="R3" t="n">
-        <v>16.60926365852356</v>
+        <v>40.80225419998169</v>
       </c>
       <c r="S3" t="n">
-        <v>16.61558747291565</v>
+        <v>32.20415949821472</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>20250515-150024</t>
+          <t>20250515-041459</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -6474,7 +7286,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -6536,62 +7348,62 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="C4" t="n">
-        <v>5233.480388402939</v>
+        <v>4764.842020273209</v>
       </c>
       <c r="D4" t="n">
-        <v>4.159999847412109</v>
+        <v>15.81999969482422</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2325431082297016</v>
+        <v>0.2752702126377507</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4735681116580963</v>
+        <v>0.6218905448913574</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4451888799667358</v>
+        <v>0.5937235355377197</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4452793598175049</v>
+        <v>0.5947504043579102</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4384709298610687</v>
+        <v>0.5806722044944763</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1401312351226806</v>
+        <v>0.1089552491903305</v>
       </c>
       <c r="K4" t="n">
-        <v>1.094522356987</v>
+        <v>4.891057014465332</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9972993135452271</v>
+        <v>2.882539510726929</v>
       </c>
       <c r="M4" t="n">
-        <v>50.48900771141052</v>
+        <v>215.2960937023163</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0398236362139384</v>
+        <v>0.0496976939837137</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0569935901959737</v>
+        <v>0.1343611256281534</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0560769526163736</v>
+        <v>0.1071430301666259</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.94709086418152</v>
+        <v>14.90930819511414</v>
       </c>
       <c r="R4" t="n">
-        <v>17.09807705879211</v>
+        <v>40.30833768844604</v>
       </c>
       <c r="S4" t="n">
-        <v>16.82308578491211</v>
+        <v>32.14290904998779</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>20250515-164819</t>
+          <t>20250515-061515</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -6601,7 +7413,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -6663,62 +7475,62 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="C5" t="n">
-        <v>5981.135018110275</v>
+        <v>5944.933463096619</v>
       </c>
       <c r="D5" t="n">
-        <v>4.699999809265137</v>
+        <v>14.44999980926514</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2284780330517712</v>
+        <v>0.2797835177563606</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4748797118663788</v>
+        <v>0.630143940448761</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4412203133106231</v>
+        <v>0.5923925638198853</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4441468715667724</v>
+        <v>0.5927668213844299</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4426465928554535</v>
+        <v>0.5806848406791687</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1430342942476272</v>
+        <v>0.1121944934129715</v>
       </c>
       <c r="K5" t="n">
-        <v>1.107426404953003</v>
+        <v>4.915107727050781</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9767404198646544</v>
+        <v>2.840914011001587</v>
       </c>
       <c r="M5" t="n">
-        <v>51.47875618934631</v>
+        <v>222.1654608249664</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0397265521685282</v>
+        <v>0.0495013872782389</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0570658739407857</v>
+        <v>0.134300041993459</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0568992940584818</v>
+        <v>0.1046868920326233</v>
       </c>
       <c r="Q5" t="n">
-        <v>11.91796565055847</v>
+        <v>14.85041618347168</v>
       </c>
       <c r="R5" t="n">
-        <v>17.11976218223572</v>
+        <v>40.29001259803772</v>
       </c>
       <c r="S5" t="n">
-        <v>17.06978821754456</v>
+        <v>31.40606760978699</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>20250515-181803</t>
+          <t>20250515-074054</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -6728,7 +7540,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -6790,62 +7602,62 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="C6" t="n">
-        <v>4622.37753534317</v>
+        <v>4986.722508430481</v>
       </c>
       <c r="D6" t="n">
-        <v>4.03000020980835</v>
+        <v>14.43000030517578</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2289086776700886</v>
+        <v>0.2840788150445009</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4760713279247284</v>
+        <v>0.625427782535553</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4462943971157074</v>
+        <v>0.5835095047950745</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4436244964599609</v>
+        <v>0.5836887359619141</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4461616277694702</v>
+        <v>0.5693891644477844</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1401428133249282</v>
+        <v>0.1093842238187789</v>
       </c>
       <c r="K6" t="n">
-        <v>1.095289349555969</v>
+        <v>4.918684959411621</v>
       </c>
       <c r="L6" t="n">
-        <v>1.016393065452576</v>
+        <v>2.833873987197876</v>
       </c>
       <c r="M6" t="n">
-        <v>51.88403058052063</v>
+        <v>219.3778202533722</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0387313508987426</v>
+        <v>0.0487260349591573</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0570101261138916</v>
+        <v>0.135168703397115</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0559830443064371</v>
+        <v>0.1036297686894734</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.6194052696228</v>
+        <v>14.61781048774719</v>
       </c>
       <c r="R6" t="n">
-        <v>17.10303783416748</v>
+        <v>40.55061101913452</v>
       </c>
       <c r="S6" t="n">
-        <v>16.79491329193115</v>
+        <v>31.08893060684204</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>20250515-200016</t>
+          <t>20250515-092619</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -6855,7 +7667,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -7093,62 +7905,62 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="C2" t="n">
-        <v>5522.828767776489</v>
+        <v>3442.77494597435</v>
       </c>
       <c r="D2" t="n">
-        <v>6.289999961853027</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2594620630871959</v>
+        <v>0.2280745281248676</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4707333147525787</v>
+        <v>0.4684184491634369</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4405121207237243</v>
+        <v>0.4380539953708648</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4406005144119262</v>
+        <v>0.4426061809062958</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4388192594051361</v>
+        <v>0.4402731657028198</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1047091409564018</v>
+        <v>0.1429133713245391</v>
       </c>
       <c r="K2" t="n">
-        <v>1.280014872550964</v>
+        <v>1.10968279838562</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9514496326446532</v>
+        <v>0.9816176891326904</v>
       </c>
       <c r="M2" t="n">
-        <v>78.95129489898682</v>
+        <v>52.45492577552795</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0384289662043253</v>
+        <v>0.0388447141647338</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0627020303408304</v>
+        <v>0.0581852316856384</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0570457251866658</v>
+        <v>0.0559592819213867</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.52868986129761</v>
+        <v>11.65341424942017</v>
       </c>
       <c r="R2" t="n">
-        <v>18.81060910224915</v>
+        <v>17.45556950569153</v>
       </c>
       <c r="S2" t="n">
-        <v>17.11371755599976</v>
+        <v>16.78778457641602</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>20250516-014310</t>
+          <t>20250515-140027</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -7158,7 +7970,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -7220,62 +8032,62 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="C3" t="n">
-        <v>4190.029001951218</v>
+        <v>6324.202313661575</v>
       </c>
       <c r="D3" t="n">
-        <v>6.289999961853027</v>
+        <v>4.019999980926514</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2617984418907473</v>
+        <v>0.2306147572067048</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4630801975727081</v>
+        <v>0.4784103631973266</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4334987699985504</v>
+        <v>0.4475007653236389</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4341419041156769</v>
+        <v>0.451127827167511</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4357408285140991</v>
+        <v>0.4486460983753204</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1037385240197181</v>
+        <v>0.1416954696178436</v>
       </c>
       <c r="K3" t="n">
-        <v>1.38692843914032</v>
+        <v>1.047324538230896</v>
       </c>
       <c r="L3" t="n">
-        <v>0.935671091079712</v>
+        <v>1.013839602470398</v>
       </c>
       <c r="M3" t="n">
-        <v>81.6419038772583</v>
+        <v>52.26185750961304</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0366013463338216</v>
+        <v>0.0375942126909891</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0650335057576497</v>
+        <v>0.0553642121950785</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0566146461168924</v>
+        <v>0.0553852915763855</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.98040390014648</v>
+        <v>11.27826380729675</v>
       </c>
       <c r="R3" t="n">
-        <v>19.51005172729492</v>
+        <v>16.60926365852356</v>
       </c>
       <c r="S3" t="n">
-        <v>16.98439383506775</v>
+        <v>16.61558747291565</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>20250516-031814</t>
+          <t>20250515-150024</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -7285,7 +8097,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -7347,62 +8159,62 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="C4" t="n">
-        <v>2542.533630847931</v>
+        <v>5233.480388402939</v>
       </c>
       <c r="D4" t="n">
-        <v>6.260000228881836</v>
+        <v>4.159999847412109</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2658263130767925</v>
+        <v>0.2325431082297016</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4325735867023468</v>
+        <v>0.4735681116580963</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4023071229457855</v>
+        <v>0.4451888799667358</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4025279879570007</v>
+        <v>0.4452793598175049</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4035296142101288</v>
+        <v>0.4384709298610687</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1039759591221809</v>
+        <v>0.1401312351226806</v>
       </c>
       <c r="K4" t="n">
-        <v>1.286860227584839</v>
+        <v>1.094522356987</v>
       </c>
       <c r="L4" t="n">
-        <v>0.960457682609558</v>
+        <v>0.9972993135452271</v>
       </c>
       <c r="M4" t="n">
-        <v>81.13152813911438</v>
+        <v>50.48900771141052</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0347255500157674</v>
+        <v>0.0398236362139384</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0622742136319478</v>
+        <v>0.0569935901959737</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0547326699892679</v>
+        <v>0.0560769526163736</v>
       </c>
       <c r="Q4" t="n">
-        <v>10.41766500473022</v>
+        <v>11.94709086418152</v>
       </c>
       <c r="R4" t="n">
-        <v>18.68226408958435</v>
+        <v>17.09807705879211</v>
       </c>
       <c r="S4" t="n">
-        <v>16.4198009967804</v>
+        <v>16.82308578491211</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>20250516-043107</t>
+          <t>20250515-164819</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -7412,7 +8224,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -7474,62 +8286,62 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="C5" t="n">
-        <v>2694.229969501496</v>
+        <v>5981.135018110275</v>
       </c>
       <c r="D5" t="n">
-        <v>6.289999961853027</v>
+        <v>4.699999809265137</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2669450961626493</v>
+        <v>0.2284780330517712</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4435779750347137</v>
+        <v>0.4748797118663788</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4120460748672485</v>
+        <v>0.4412203133106231</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4135923087596893</v>
+        <v>0.4441468715667724</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4112617373466491</v>
+        <v>0.4426465928554535</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1071904227137565</v>
+        <v>0.1430342942476272</v>
       </c>
       <c r="K5" t="n">
-        <v>1.26441216468811</v>
+        <v>1.107426404953003</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9452008008956908</v>
+        <v>0.9767404198646544</v>
       </c>
       <c r="M5" t="n">
-        <v>81.98952460289001</v>
+        <v>51.47875618934631</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0364480392138163</v>
+        <v>0.0397265521685282</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0608704813321431</v>
+        <v>0.0570658739407857</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0564072442054748</v>
+        <v>0.0568992940584818</v>
       </c>
       <c r="Q5" t="n">
-        <v>10.9344117641449</v>
+        <v>11.91796565055847</v>
       </c>
       <c r="R5" t="n">
-        <v>18.26114439964294</v>
+        <v>17.11976218223572</v>
       </c>
       <c r="S5" t="n">
-        <v>16.92217326164246</v>
+        <v>17.06978821754456</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>20250516-051631</t>
+          <t>20250515-181803</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -7539,7 +8351,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -7601,62 +8413,62 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C6" t="n">
-        <v>4848.182167768478</v>
+        <v>4622.37753534317</v>
       </c>
       <c r="D6" t="n">
-        <v>6.320000171661377</v>
+        <v>4.03000020980835</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2581732109602954</v>
+        <v>0.2289086776700886</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4621203541755676</v>
+        <v>0.4760713279247284</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4262866079807281</v>
+        <v>0.4462943971157074</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4286003410816192</v>
+        <v>0.4436244964599609</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4283034205436706</v>
+        <v>0.4461616277694702</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1067229509353637</v>
+        <v>0.1401428133249282</v>
       </c>
       <c r="K6" t="n">
-        <v>1.279324531555176</v>
+        <v>1.095289349555969</v>
       </c>
       <c r="L6" t="n">
-        <v>0.916375994682312</v>
+        <v>1.016393065452576</v>
       </c>
       <c r="M6" t="n">
-        <v>79.92505168914795</v>
+        <v>51.88403058052063</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0363328719139099</v>
+        <v>0.0387313508987426</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0631328503290812</v>
+        <v>0.0570101261138916</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0556595118840535</v>
+        <v>0.0559830443064371</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.89986157417297</v>
+        <v>11.6194052696228</v>
       </c>
       <c r="R6" t="n">
-        <v>18.93985509872437</v>
+        <v>17.10303783416748</v>
       </c>
       <c r="S6" t="n">
-        <v>16.69785356521606</v>
+        <v>16.79491329193115</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>20250516-060427</t>
+          <t>20250515-200016</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -7666,7 +8478,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -7904,62 +8716,62 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="C2" t="n">
-        <v>4794.406268835068</v>
+        <v>5522.828767776489</v>
       </c>
       <c r="D2" t="n">
-        <v>11.9399995803833</v>
+        <v>6.289999961853027</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2841110188227433</v>
+        <v>0.2594620630871959</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5770745277404785</v>
+        <v>0.4707333147525787</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5422368049621582</v>
+        <v>0.4405121207237243</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5460788607597351</v>
+        <v>0.4406005144119262</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5420780181884766</v>
+        <v>0.4388192594051361</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0716026872396469</v>
+        <v>0.1047091409564018</v>
       </c>
       <c r="K2" t="n">
-        <v>5.258383750915527</v>
+        <v>1.280014872550964</v>
       </c>
       <c r="L2" t="n">
-        <v>1.68167245388031</v>
+        <v>0.9514496326446532</v>
       </c>
       <c r="M2" t="n">
-        <v>146.0034608840942</v>
+        <v>78.95129489898682</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0435478560129801</v>
+        <v>0.0384289662043253</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1339227048556009</v>
+        <v>0.0627020303408304</v>
       </c>
       <c r="P2" t="n">
-        <v>0.07840474685033159</v>
+        <v>0.0570457251866658</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.06435680389404</v>
+        <v>11.52868986129761</v>
       </c>
       <c r="R2" t="n">
-        <v>40.1768114566803</v>
+        <v>18.81060910224915</v>
       </c>
       <c r="S2" t="n">
-        <v>23.52142405509949</v>
+        <v>17.11371755599976</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>20250516-165650</t>
+          <t>20250516-014310</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -7969,7 +8781,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -8031,62 +8843,62 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C3" t="n">
-        <v>4343.945487260818</v>
+        <v>4190.029001951218</v>
       </c>
       <c r="D3" t="n">
-        <v>12.60000038146973</v>
+        <v>6.289999961853027</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2864224829916226</v>
+        <v>0.2617984418907473</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5878122448921204</v>
+        <v>0.4630801975727081</v>
       </c>
       <c r="G3" t="n">
-        <v>0.551874577999115</v>
+        <v>0.4334987699985504</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5509212017059326</v>
+        <v>0.4341419041156769</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5485839247703552</v>
+        <v>0.4357408285140991</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0829284340143203</v>
+        <v>0.1037385240197181</v>
       </c>
       <c r="K3" t="n">
-        <v>5.246112823486328</v>
+        <v>1.38692843914032</v>
       </c>
       <c r="L3" t="n">
-        <v>1.688726902008057</v>
+        <v>0.935671091079712</v>
       </c>
       <c r="M3" t="n">
-        <v>146.8677237033844</v>
+        <v>81.6419038772583</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0441620326042175</v>
+        <v>0.0366013463338216</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1333455069859822</v>
+        <v>0.0650335057576497</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0770759717623392</v>
+        <v>0.0566146461168924</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.24860978126526</v>
+        <v>10.98040390014648</v>
       </c>
       <c r="R3" t="n">
-        <v>40.00365209579468</v>
+        <v>19.51005172729492</v>
       </c>
       <c r="S3" t="n">
-        <v>23.12279152870178</v>
+        <v>16.98439383506775</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>20250516-182138</t>
+          <t>20250516-031814</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -8096,7 +8908,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -8158,62 +8970,62 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="C4" t="n">
-        <v>4498.906786203384</v>
+        <v>2542.533630847931</v>
       </c>
       <c r="D4" t="n">
-        <v>11.61999988555908</v>
+        <v>6.260000228881836</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2865507846972981</v>
+        <v>0.2658263130767925</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5879257321357727</v>
+        <v>0.4325735867023468</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5532993078231812</v>
+        <v>0.4023071229457855</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5491756796836853</v>
+        <v>0.4025279879570007</v>
       </c>
       <c r="I4" t="n">
-        <v>0.543567955493927</v>
+        <v>0.4035296142101288</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0701100155711174</v>
+        <v>0.1039759591221809</v>
       </c>
       <c r="K4" t="n">
-        <v>5.230305671691895</v>
+        <v>1.286860227584839</v>
       </c>
       <c r="L4" t="n">
-        <v>1.696790933609009</v>
+        <v>0.960457682609558</v>
       </c>
       <c r="M4" t="n">
-        <v>145.3453030586243</v>
+        <v>81.13152813911438</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0426802158355712</v>
+        <v>0.0347255500157674</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1327937658627828</v>
+        <v>0.0622742136319478</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0769743720690409</v>
+        <v>0.0547326699892679</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.80406475067139</v>
+        <v>10.41766500473022</v>
       </c>
       <c r="R4" t="n">
-        <v>39.83812975883484</v>
+        <v>18.68226408958435</v>
       </c>
       <c r="S4" t="n">
-        <v>23.09231162071228</v>
+        <v>16.4198009967804</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>20250516-193856</t>
+          <t>20250516-043107</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -8223,7 +9035,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -8285,62 +9097,62 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="C5" t="n">
-        <v>4878.853821277618</v>
+        <v>2694.229969501496</v>
       </c>
       <c r="D5" t="n">
-        <v>13.64000034332275</v>
+        <v>6.289999961853027</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2857863234751152</v>
+        <v>0.2669450961626493</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5889156460762024</v>
+        <v>0.4435779750347137</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5495288372039795</v>
+        <v>0.4120460748672485</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5470798015594482</v>
+        <v>0.4135923087596893</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5443153381347656</v>
+        <v>0.4112617373466491</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0725391879677772</v>
+        <v>0.1071904227137565</v>
       </c>
       <c r="K5" t="n">
-        <v>5.176760196685791</v>
+        <v>1.26441216468811</v>
       </c>
       <c r="L5" t="n">
-        <v>1.663674473762512</v>
+        <v>0.9452008008956908</v>
       </c>
       <c r="M5" t="n">
-        <v>145.2971835136414</v>
+        <v>81.98952460289001</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0447913265228271</v>
+        <v>0.0364480392138163</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1324799116452535</v>
+        <v>0.0608704813321431</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0781792426109314</v>
+        <v>0.0564072442054748</v>
       </c>
       <c r="Q5" t="n">
-        <v>13.43739795684814</v>
+        <v>10.9344117641449</v>
       </c>
       <c r="R5" t="n">
-        <v>39.74397349357605</v>
+        <v>18.26114439964294</v>
       </c>
       <c r="S5" t="n">
-        <v>23.45377278327942</v>
+        <v>16.92217326164246</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>20250516-205846</t>
+          <t>20250516-051631</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -8350,7 +9162,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -8412,62 +9224,62 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="C6" t="n">
-        <v>3419.18400478363</v>
+        <v>4848.182167768478</v>
       </c>
       <c r="D6" t="n">
-        <v>10.32999992370606</v>
+        <v>6.320000171661377</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2865352805541909</v>
+        <v>0.2581732109602954</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5766639113426208</v>
+        <v>0.4621203541755676</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5405468940734863</v>
+        <v>0.4262866079807281</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5410169363021851</v>
+        <v>0.4286003410816192</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5382978916168213</v>
+        <v>0.4283034205436706</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0794805660843849</v>
+        <v>0.1067229509353637</v>
       </c>
       <c r="K6" t="n">
-        <v>5.217320919036865</v>
+        <v>1.279324531555176</v>
       </c>
       <c r="L6" t="n">
-        <v>1.687687516212463</v>
+        <v>0.916375994682312</v>
       </c>
       <c r="M6" t="n">
-        <v>148.0659284591675</v>
+        <v>79.92505168914795</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0444955309232076</v>
+        <v>0.0363328719139099</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1319986001650492</v>
+        <v>0.0631328503290812</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0774227738380432</v>
+        <v>0.0556595118840535</v>
       </c>
       <c r="Q6" t="n">
-        <v>13.34865927696228</v>
+        <v>10.89986157417297</v>
       </c>
       <c r="R6" t="n">
-        <v>39.59958004951477</v>
+        <v>18.93985509872437</v>
       </c>
       <c r="S6" t="n">
-        <v>23.22683215141296</v>
+        <v>16.69785356521606</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>20250516-222457</t>
+          <t>20250516-060427</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -8477,7 +9289,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -8715,62 +9527,62 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C2" t="n">
-        <v>3769.914018630981</v>
+        <v>4794.406268835068</v>
       </c>
       <c r="D2" t="n">
-        <v>7.809999942779541</v>
+        <v>11.9399995803833</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2099228995541731</v>
+        <v>0.2841110188227433</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5128582119941711</v>
+        <v>0.5770745277404785</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4817813634872436</v>
+        <v>0.5422368049621582</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4831418693065643</v>
+        <v>0.5460788607597351</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4801167249679565</v>
+        <v>0.5420780181884766</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0829966366291046</v>
+        <v>0.0716026872396469</v>
       </c>
       <c r="K2" t="n">
-        <v>1.258856058120728</v>
+        <v>5.258383750915527</v>
       </c>
       <c r="L2" t="n">
-        <v>1.035138845443726</v>
+        <v>1.68167245388031</v>
       </c>
       <c r="M2" t="n">
-        <v>59.08326888084412</v>
+        <v>146.0034608840942</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0350144664446512</v>
+        <v>0.0435478560129801</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0627606201171875</v>
+        <v>0.1339227048556009</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0595352506637573</v>
+        <v>0.07840474685033159</v>
       </c>
       <c r="Q2" t="n">
-        <v>10.50433993339539</v>
+        <v>13.06435680389404</v>
       </c>
       <c r="R2" t="n">
-        <v>18.82818603515625</v>
+        <v>40.1768114566803</v>
       </c>
       <c r="S2" t="n">
-        <v>17.8605751991272</v>
+        <v>23.52142405509949</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>20250509-045803</t>
+          <t>20250516-165650</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -8780,7 +9592,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>yolox_s</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -8800,7 +9612,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>97feded0d</t>
+          <t>f3410bbc1</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -8810,7 +9622,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>97feded0d</t>
+          <t>f3410bbc1</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -8842,62 +9654,62 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="C3" t="n">
-        <v>5086.055543661118</v>
+        <v>4343.945487260818</v>
       </c>
       <c r="D3" t="n">
-        <v>9.75</v>
+        <v>12.60000038146973</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2083594913942268</v>
+        <v>0.2864224829916226</v>
       </c>
       <c r="F3" t="n">
-        <v>0.52392578125</v>
+        <v>0.5878122448921204</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4936708807945251</v>
+        <v>0.551874577999115</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4936651885509491</v>
+        <v>0.5509212017059326</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4914116263389587</v>
+        <v>0.5485839247703552</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0859270095825195</v>
+        <v>0.0829284340143203</v>
       </c>
       <c r="K3" t="n">
-        <v>1.26954996585846</v>
+        <v>5.246112823486328</v>
       </c>
       <c r="L3" t="n">
-        <v>1.080401420593261</v>
+        <v>1.688726902008057</v>
       </c>
       <c r="M3" t="n">
-        <v>58.35318040847778</v>
+        <v>146.8677237033844</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0364483650525411</v>
+        <v>0.0441620326042175</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0634031629562378</v>
+        <v>0.1333455069859822</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0611013825734456</v>
+        <v>0.0770759717623392</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.93450951576233</v>
+        <v>13.24860978126526</v>
       </c>
       <c r="R3" t="n">
-        <v>19.02094888687133</v>
+        <v>40.00365209579468</v>
       </c>
       <c r="S3" t="n">
-        <v>18.33041477203369</v>
+        <v>23.12279152870178</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>20250509-060335</t>
+          <t>20250516-182138</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -8907,7 +9719,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>yolox_s</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -8927,7 +9739,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>97feded0d</t>
+          <t>f3410bbc1</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -8937,7 +9749,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>97feded0d</t>
+          <t>f3410bbc1</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -8969,62 +9781,62 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C4" t="n">
-        <v>3482.002310276031</v>
+        <v>4498.906786203384</v>
       </c>
       <c r="D4" t="n">
-        <v>8.800000190734863</v>
+        <v>11.61999988555908</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2111128784183945</v>
+        <v>0.2865507846972981</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5099393129348755</v>
+        <v>0.5879257321357727</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4790474474430084</v>
+        <v>0.5532993078231812</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4799931943416595</v>
+        <v>0.5491756796836853</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4775107204914093</v>
+        <v>0.543567955493927</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0875294283032417</v>
+        <v>0.0701100155711174</v>
       </c>
       <c r="K4" t="n">
-        <v>1.262146353721619</v>
+        <v>5.230305671691895</v>
       </c>
       <c r="L4" t="n">
-        <v>1.04424238204956</v>
+        <v>1.696790933609009</v>
       </c>
       <c r="M4" t="n">
-        <v>60.39233493804932</v>
+        <v>145.3453030586243</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0343831793467203</v>
+        <v>0.0426802158355712</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06392911672592159</v>
+        <v>0.1327937658627828</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0593721763292948</v>
+        <v>0.0769743720690409</v>
       </c>
       <c r="Q4" t="n">
-        <v>10.31495380401611</v>
+        <v>12.80406475067139</v>
       </c>
       <c r="R4" t="n">
-        <v>19.17873501777649</v>
+        <v>39.83812975883484</v>
       </c>
       <c r="S4" t="n">
-        <v>17.81165289878845</v>
+        <v>23.09231162071228</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>20250509-073103</t>
+          <t>20250516-193856</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -9034,7 +9846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>yolox_s</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -9054,7 +9866,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>97feded0d</t>
+          <t>f3410bbc1</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -9064,7 +9876,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>97feded0d</t>
+          <t>f3410bbc1</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -9096,62 +9908,62 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="C5" t="n">
-        <v>4894.750937700272</v>
+        <v>4878.853821277618</v>
       </c>
       <c r="D5" t="n">
-        <v>9.020000457763672</v>
+        <v>13.64000034332275</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2063441587612033</v>
+        <v>0.2857863234751152</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5092978477478027</v>
+        <v>0.5889156460762024</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4746448695659637</v>
+        <v>0.5495288372039795</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4786581695079803</v>
+        <v>0.5470798015594482</v>
       </c>
       <c r="I5" t="n">
-        <v>0.474529355764389</v>
+        <v>0.5443153381347656</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0810377821326255</v>
+        <v>0.0725391879677772</v>
       </c>
       <c r="K5" t="n">
-        <v>1.338886857032776</v>
+        <v>5.176760196685791</v>
       </c>
       <c r="L5" t="n">
-        <v>1.06293535232544</v>
+        <v>1.663674473762512</v>
       </c>
       <c r="M5" t="n">
-        <v>58.31261396408081</v>
+        <v>145.2971835136414</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0343996143341064</v>
+        <v>0.0447913265228271</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0655732154846191</v>
+        <v>0.1324799116452535</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0612890243530273</v>
+        <v>0.0781792426109314</v>
       </c>
       <c r="Q5" t="n">
-        <v>10.31988430023193</v>
+        <v>13.43739795684814</v>
       </c>
       <c r="R5" t="n">
-        <v>19.67196464538575</v>
+        <v>39.74397349357605</v>
       </c>
       <c r="S5" t="n">
-        <v>18.3867073059082</v>
+        <v>23.45377278327942</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>20250509-083147</t>
+          <t>20250516-205846</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -9161,7 +9973,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>yolox_s</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -9181,7 +9993,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>97feded0d</t>
+          <t>f3410bbc1</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -9191,7 +10003,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>97feded0d</t>
+          <t>f3410bbc1</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -9223,62 +10035,62 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C6" t="n">
-        <v>3476.170988798141</v>
+        <v>3419.18400478363</v>
       </c>
       <c r="D6" t="n">
-        <v>6.019999980926514</v>
+        <v>10.32999992370606</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2091836777648755</v>
+        <v>0.2865352805541909</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5107935667037964</v>
+        <v>0.5766639113426208</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4730213582515716</v>
+        <v>0.5405468940734863</v>
       </c>
       <c r="H6" t="n">
-        <v>0.476974606513977</v>
+        <v>0.5410169363021851</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4722312688827514</v>
+        <v>0.5382978916168213</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0856380313634872</v>
+        <v>0.0794805660843849</v>
       </c>
       <c r="K6" t="n">
-        <v>1.247788906097412</v>
+        <v>5.217320919036865</v>
       </c>
       <c r="L6" t="n">
-        <v>1.058021545410156</v>
+        <v>1.687687516212463</v>
       </c>
       <c r="M6" t="n">
-        <v>60.08119416236877</v>
+        <v>148.0659284591675</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0353939541180928</v>
+        <v>0.0444955309232076</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0639199225107828</v>
+        <v>0.1319986001650492</v>
       </c>
       <c r="P6" t="n">
-        <v>0.059868570168813</v>
+        <v>0.0774227738380432</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.61818623542786</v>
+        <v>13.34865927696228</v>
       </c>
       <c r="R6" t="n">
-        <v>19.17597675323486</v>
+        <v>39.59958004951477</v>
       </c>
       <c r="S6" t="n">
-        <v>17.96057105064392</v>
+        <v>23.22683215141296</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>20250509-095604</t>
+          <t>20250516-222457</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -9288,7 +10100,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>yolox_s</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -9308,7 +10120,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>97feded0d</t>
+          <t>f3410bbc1</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -9318,7 +10130,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>97feded0d</t>
+          <t>f3410bbc1</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
